--- a/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/G15-会前签认跟踪-20260924-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/G15-会前签认跟踪-20260924-V1.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12660" activeTab="2"/>
+    <workbookView windowWidth="28260" windowHeight="12660" activeTab="0"/>
   </bookViews>
   <sheets>
+    <sheet name="使用说明" sheetId="3" r:id="rId3"/>
     <sheet name="签认跟踪" sheetId="1" r:id="rId1"/>
     <sheet name="会前材料" sheetId="2" r:id="rId2"/>
-    <sheet name="使用说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">签认跟踪!$A$6:$K$13</definedName>
@@ -119,7 +119,7 @@
     <t>待确认</t>
   </si>
   <si>
-    <t>确认计划人天唯一来源为《月度投入明细》：5,433 人天 / 769.77 万元 / 均价 1,416.84 元（G15 会前完成）</t>
+    <t>确认计划人天唯一来源为《月度投入明细》：4,721 人天 / 652.57 万元 / 均价 1,382.27 元（G15 会前完成）</t>
   </si>
   <si>
     <t>人工成本预算、月度投入明细、成本总览（05 成本工作簿）</t>
@@ -1446,7 +1446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
@@ -1763,7 +1763,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:K13" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A6:K13">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="F7:F13">
@@ -1787,7 +1787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
@@ -1973,7 +1973,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:G10" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A4:G10">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/G15-会前签认跟踪-20260924-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/G15-会前签认跟踪-20260924-V1.xlsx
@@ -119,7 +119,7 @@
     <t>待确认</t>
   </si>
   <si>
-    <t>确认计划人天唯一来源为《月度投入明细》：4,721 人天 / 652.57 万元 / 均价 1,382.27 元（G15 会前完成）</t>
+    <t>确认计划人天唯一来源为《月度投入明细》：4,337 人天 / 607.09 万元 / 均价 1,399.79 元（G15 会前完成）</t>
   </si>
   <si>
     <t>人工成本预算、月度投入明细、成本总览（05 成本工作簿）</t>
